--- a/Relacion FMC - APR.xlsx
+++ b/Relacion FMC - APR.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x16267\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{246AEBF1-0EC1-4DBE-9A04-4FB29DA0D605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A14D1A3-45F2-462F-BBD0-58CE230AA219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4DE66A40-4DB2-4A1B-B36C-1BC10B84D212}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="343">
   <si>
     <t>APLICATIVO</t>
   </si>
@@ -1026,6 +1023,51 @@
   </si>
   <si>
     <t>2101</t>
+  </si>
+  <si>
+    <t>Líneas de crédito por convenio (Parte 2)</t>
+  </si>
+  <si>
+    <t>Leasing</t>
+  </si>
+  <si>
+    <t>Mercado de Capitales</t>
+  </si>
+  <si>
+    <t>Mediana y Pequeña Empresa</t>
+  </si>
+  <si>
+    <t>Pago Activo Pagos</t>
+  </si>
+  <si>
+    <t>Cartas fianza</t>
+  </si>
+  <si>
+    <t>Told II</t>
+  </si>
+  <si>
+    <t>Systematics-Impacs</t>
+  </si>
+  <si>
+    <t>Systematics-Saving Times</t>
+  </si>
+  <si>
+    <t>BankTrade</t>
+  </si>
+  <si>
+    <t>Sistema de Administración de Tarjetas - NSAT</t>
+  </si>
+  <si>
+    <t>Financiamiento de cobranza de documentos</t>
+  </si>
+  <si>
+    <t>Garantías y custodia</t>
+  </si>
+  <si>
+    <t>Judicial Condonación y Castigo</t>
+  </si>
+  <si>
+    <t>Hipotecario y créditos de consumo</t>
   </si>
 </sst>
 </file>
@@ -1109,9 +1151,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1136,6 +1175,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1151,541 +1193,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Relacion FMC - APR"/>
-      <sheetName val="Hoja1"/>
-      <sheetName val="Tablas-Campos"/>
-      <sheetName val="Tablas RNT"/>
-      <sheetName val="Detalles"/>
-      <sheetName val="Relacion_tablas"/>
-      <sheetName val="Detalle_tablas"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>Siglas</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Aplicativo que corresponde</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Aplicativo</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>WBC</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>WBC</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>WF Banca Comercial</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TLD</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>TLD</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>Told II</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>$ST</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>$ST</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>Systematics-Saving Times</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>$IM</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>$IM</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>Systematics-Impacs</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>SCF</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>SCF</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>Cartas fianza</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>PRO</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>PRO</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>Provisiones</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>PPA</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>PPA</v>
-          </cell>
-          <cell r="D8" t="str">
-            <v>Pago Activo Pagos</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>MYP</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>MYP</v>
-          </cell>
-          <cell r="D9" t="str">
-            <v>Mediana y Pequeña Empresa</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>MDC</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>MDC</v>
-          </cell>
-          <cell r="D10" t="str">
-            <v>Mercado de Capitales</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>LPC</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>LPC</v>
-          </cell>
-          <cell r="D11" t="str">
-            <v>Leasing</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>LID</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>LIC</v>
-          </cell>
-          <cell r="D12" t="str">
-            <v>Líneas de crédito por convenio (Parte 1)</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>LIC</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>LIC</v>
-          </cell>
-          <cell r="D13" t="str">
-            <v>Líneas de crédito por convenio (Parte 2)</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>JCC</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>JCC</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>Judicial Condonación y Castigo</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>HIP</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>HPC</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>Hipotecario y créditos de consumo (Parte 1)</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>GAC</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>GAC</v>
-          </cell>
-          <cell r="D16" t="str">
-            <v>Garantías y custodia</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>FMU</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>FMU</v>
-          </cell>
-          <cell r="D17" t="str">
-            <v>Fondos mutuos</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>FCD</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>FCD</v>
-          </cell>
-          <cell r="D18" t="str">
-            <v>Financiamiento de cobranza de documentos</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>CNS</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>HPC</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>Hipotecario y créditos de consumo (Parte 2)</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>CDO</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>SAT</v>
-          </cell>
-          <cell r="D20" t="str">
-            <v>Sistema de Administración de Tarjetas - NSAT</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>BKT</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>BKT</v>
-          </cell>
-          <cell r="D21" t="str">
-            <v>BankTrade</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>ADJ</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>ADJ</v>
-          </cell>
-          <cell r="D22" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>REJ</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>REJ</v>
-          </cell>
-          <cell r="D23" t="str">
-            <v>Retenciones Judiciales</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>$IT</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>$IT</v>
-          </cell>
-          <cell r="D24" t="str">
-            <v>Systematics-Intersystem Transfers</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>RNC</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>RNC</v>
-          </cell>
-          <cell r="D25" t="str">
-            <v>Cajeros Global Net</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>AR</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>AR</v>
-          </cell>
-          <cell r="D26" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>BKD</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>BKD</v>
-          </cell>
-          <cell r="D27" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>DEP</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>DEP</v>
-          </cell>
-          <cell r="D28" t="str">
-            <v>Depósitos</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>SAT</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>SAT</v>
-          </cell>
-          <cell r="D29" t="str">
-            <v>Sistema de Administración de Tarjetas (antiguo)</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>CCD</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>CCD</v>
-          </cell>
-          <cell r="D30" t="str">
-            <v>Core de Créditos Digital</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>BSE</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>BSE</v>
-          </cell>
-          <cell r="D31" t="str">
-            <v>Bus de servicios Interbank (MultiBus)</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>ITB</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>ITB</v>
-          </cell>
-          <cell r="D32" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>PAG</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>PAG</v>
-          </cell>
-          <cell r="D33" t="str">
-            <v>Pago Activo Cobros</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>INC</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>INC</v>
-          </cell>
-          <cell r="D34" t="str">
-            <v>Incoming</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>ITF</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>ITF</v>
-          </cell>
-          <cell r="D35" t="str">
-            <v>Impuesto a las Transacciones Bancarias</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>HPC</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>HPC</v>
-          </cell>
-          <cell r="D36" t="str">
-            <v>Hipotecario y créditos de consumo</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>LBC</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>LBC</v>
-          </cell>
-          <cell r="D37" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>EBS</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>EBS</v>
-          </cell>
-          <cell r="D38" t="str">
-            <v>Enterprise business suite</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>AP</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>AP</v>
-          </cell>
-          <cell r="D39" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>CBA</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>CBA</v>
-          </cell>
-          <cell r="D40" t="str">
-            <v>Conciliación Bancaria</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>TMF</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>TMF</v>
-          </cell>
-          <cell r="D41" t="str">
-            <v>Transferencia Masiva de Fondos</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>IPG</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>IPG</v>
-          </cell>
-          <cell r="D42" t="str">
-            <v>Recaudación y Pagos</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>CJE</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>CJE</v>
-          </cell>
-          <cell r="D43" t="str">
-            <v>Canje electrónico (N-Compass - NCR)</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="str">
-            <v>REV</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>REV</v>
-          </cell>
-          <cell r="D44" t="str">
-            <v>Sin Descripción</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>EDP</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>EDP</v>
-          </cell>
-          <cell r="D45" t="str">
-            <v>Remesas del exterior</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>WHP</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>WHP</v>
-          </cell>
-          <cell r="D46" t="str">
-            <v>Workflow Hipotecario Intranet/Extranet</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2011,9 +1518,9 @@
     <col min="1" max="1" width="18.26953125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.90625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.453125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="30.453125" style="5" customWidth="1"/>
     <col min="5" max="5" width="26.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="35.54296875" style="6" customWidth="1"/>
+    <col min="6" max="7" width="35.54296875" style="5" customWidth="1"/>
     <col min="8" max="8" width="17.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.6328125" style="3" bestFit="1" customWidth="1"/>
@@ -2041,53 +1548,52 @@
       <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <f>VLOOKUP(B2,[1]Hoja1!B:D,3,0)</f>
-        <v>Líneas de crédito por convenio (Parte 2)</v>
+      <c r="G2" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>620</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -2104,22 +1610,22 @@
       <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -2145,16 +1651,16 @@
       <c r="C7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -2163,7 +1669,7 @@
       <c r="I7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K7" s="3" t="s">
@@ -2174,22 +1680,22 @@
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
@@ -2198,22 +1704,22 @@
       <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -2230,22 +1736,22 @@
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
@@ -2271,16 +1777,16 @@
       <c r="C13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="3" t="s">
@@ -2289,7 +1795,7 @@
       <c r="I13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K13" s="3" t="s">
@@ -2300,22 +1806,22 @@
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
@@ -2324,22 +1830,22 @@
       <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -2356,22 +1862,22 @@
       <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
@@ -2397,16 +1903,16 @@
       <c r="C19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H19" s="3" t="s">
@@ -2415,7 +1921,7 @@
       <c r="I19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K19" s="3" t="s">
@@ -2438,29 +1944,28 @@
       <c r="F21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="2" t="str">
-        <f>VLOOKUP(B21,[1]Hoja1!B:D,3,0)</f>
-        <v>Leasing</v>
+      <c r="G21" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="6"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
@@ -2478,10 +1983,10 @@
       <c r="E24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="3" t="s">
@@ -2507,10 +2012,10 @@
       <c r="E25" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H25" t="s">
@@ -2530,16 +2035,16 @@
       <c r="C26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>57</v>
       </c>
       <c r="H26" s="3" t="s">
@@ -2553,20 +2058,20 @@
       <c r="A28" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="6"/>
+      <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
@@ -2584,10 +2089,10 @@
       <c r="E30" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>61</v>
       </c>
       <c r="H30" s="3" t="s">
@@ -2613,10 +2118,10 @@
       <c r="E31" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H31" t="s">
@@ -2636,16 +2141,16 @@
       <c r="C32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="3" t="s">
@@ -2659,20 +2164,20 @@
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="6"/>
+      <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
@@ -2690,10 +2195,10 @@
       <c r="E36" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H36" s="3" t="s">
@@ -2719,10 +2224,10 @@
       <c r="E37" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="9" t="s">
         <v>21</v>
       </c>
       <c r="H37" t="s">
@@ -2742,16 +2247,16 @@
       <c r="C38" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="5" t="s">
         <v>57</v>
       </c>
       <c r="H38" s="3" t="s">
@@ -2777,26 +2282,25 @@
       <c r="F40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G40" s="2" t="str">
-        <f>VLOOKUP(B40,[1]Hoja1!B:D,3,0)</f>
-        <v>Mercado de Capitales</v>
+      <c r="G40" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2807,10 +2311,10 @@
       <c r="B43" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2846,17 +2350,17 @@
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2867,10 +2371,10 @@
       <c r="B49" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2906,20 +2410,20 @@
       <c r="A53" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
@@ -2931,7 +2435,7 @@
       <c r="C55" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2979,30 +2483,29 @@
       <c r="F59" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G59" s="2" t="str">
-        <f>VLOOKUP(B59,[1]Hoja1!B:D,3,0)</f>
-        <v>Mediana y Pequeña Empresa</v>
+      <c r="G59" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
       <c r="AD60" s="3"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C61" s="6"/>
+      <c r="C61" s="5"/>
       <c r="AD61" s="3"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.35">
@@ -3021,10 +2524,10 @@
       <c r="E62" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="5" t="s">
         <v>93</v>
       </c>
       <c r="H62" s="3" t="s">
@@ -3045,34 +2548,34 @@
       <c r="A63" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="6" t="s">
         <v>98</v>
       </c>
       <c r="H63" t="s">
         <v>20</v>
       </c>
-      <c r="I63" s="7" t="s">
+      <c r="I63" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="J63" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="6" t="s">
         <v>100</v>
       </c>
       <c r="AD63" s="3"/>
@@ -3087,16 +2590,16 @@
       <c r="C64" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="5" t="s">
         <v>58</v>
       </c>
       <c r="H64" s="3" t="s">
@@ -3120,21 +2623,21 @@
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
       <c r="AD66" s="3"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="6"/>
+      <c r="C67" s="5"/>
       <c r="AD67" s="3"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.35">
@@ -3153,10 +2656,10 @@
       <c r="E68" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G68" s="5" t="s">
         <v>93</v>
       </c>
       <c r="H68" s="3" t="s">
@@ -3177,34 +2680,34 @@
       <c r="A69" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="G69" s="6" t="s">
         <v>98</v>
       </c>
       <c r="H69" t="s">
         <v>20</v>
       </c>
-      <c r="I69" s="7" t="s">
+      <c r="I69" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J69" s="7" t="s">
+      <c r="J69" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="AD69" s="3"/>
@@ -3219,16 +2722,16 @@
       <c r="C70" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="G70" s="5" t="s">
         <v>58</v>
       </c>
       <c r="H70" s="3" t="s">
@@ -3252,21 +2755,21 @@
       <c r="A72" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
       <c r="AD72" s="3"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="6"/>
+      <c r="C73" s="5"/>
       <c r="AD73" s="3"/>
     </row>
     <row r="74" spans="1:30" x14ac:dyDescent="0.35">
@@ -3285,10 +2788,10 @@
       <c r="E74" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G74" s="6" t="s">
+      <c r="G74" s="5" t="s">
         <v>93</v>
       </c>
       <c r="H74" s="3" t="s">
@@ -3309,34 +2812,34 @@
       <c r="A75" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="6" t="s">
         <v>98</v>
       </c>
       <c r="H75" t="s">
         <v>20</v>
       </c>
-      <c r="I75" s="7" t="s">
+      <c r="I75" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="J75" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K75" s="7" t="s">
+      <c r="K75" s="6" t="s">
         <v>100</v>
       </c>
       <c r="AD75" s="3"/>
@@ -3351,16 +2854,16 @@
       <c r="C76" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="5" t="s">
         <v>58</v>
       </c>
       <c r="H76" s="3" t="s">
@@ -3396,50 +2899,49 @@
       <c r="F78" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G78" s="2" t="str">
-        <f>VLOOKUP(B78,[1]Hoja1!B:D,3,0)</f>
-        <v>Pago Activo Pagos</v>
+      <c r="G78" s="2" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="8" t="s">
         <v>116</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G81" s="5" t="s">
         <v>96</v>
       </c>
       <c r="H81" s="3" t="s">
@@ -3465,10 +2967,10 @@
       <c r="E82" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H82" s="3" t="s">
@@ -3511,20 +3013,20 @@
       <c r="A85" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
@@ -3536,16 +3038,16 @@
       <c r="C87" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F87" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="G87" s="5" t="s">
         <v>96</v>
       </c>
       <c r="H87" s="3" t="s">
@@ -3571,10 +3073,10 @@
       <c r="E88" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G88" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H88" s="3" t="s">
@@ -3617,20 +3119,20 @@
       <c r="A91" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
@@ -3642,16 +3144,16 @@
       <c r="C93" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="5" t="s">
         <v>135</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G93" s="6" t="s">
+      <c r="G93" s="5" t="s">
         <v>137</v>
       </c>
       <c r="H93" s="3" t="s">
@@ -3671,16 +3173,16 @@
       <c r="C94" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="5" t="s">
         <v>140</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G94" s="6" t="s">
+      <c r="G94" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H94" s="3" t="s">
@@ -3735,29 +3237,28 @@
       <c r="F97" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G97" s="2" t="str">
-        <f>VLOOKUP(B97,[1]Hoja1!B:D,3,0)</f>
-        <v>Cartas fianza</v>
+      <c r="G97" s="2" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C99" s="6"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
@@ -3769,16 +3270,16 @@
       <c r="C100" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="5" t="s">
         <v>145</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="F100" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="G100" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H100" s="3" t="s">
@@ -3795,16 +3296,16 @@
       <c r="C101" t="s">
         <v>148</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F101" s="10" t="s">
+      <c r="F101" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G101" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H101" t="s">
@@ -3830,7 +3331,7 @@
       <c r="F102" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="G102" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H102" s="3" t="s">
@@ -3841,20 +3342,20 @@
       <c r="A104" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="18"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C105" s="6"/>
+      <c r="C105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
@@ -3866,16 +3367,16 @@
       <c r="C106" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="5" t="s">
         <v>145</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F106" s="6" t="s">
+      <c r="F106" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G106" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H106" s="3" t="s">
@@ -3892,16 +3393,16 @@
       <c r="C107" t="s">
         <v>148</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F107" s="10" t="s">
+      <c r="F107" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G107" s="6" t="s">
+      <c r="G107" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H107" t="s">
@@ -3927,7 +3428,7 @@
       <c r="F108" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G108" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H108" s="3" t="s">
@@ -3938,20 +3439,20 @@
       <c r="A110" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C111" s="6"/>
+      <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
@@ -3963,16 +3464,16 @@
       <c r="C112" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="5" t="s">
         <v>157</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F112" s="6" t="s">
+      <c r="F112" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G112" s="6" t="s">
+      <c r="G112" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H112" s="3" t="s">
@@ -3989,16 +3490,16 @@
       <c r="C113" t="s">
         <v>148</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F113" s="10" t="s">
+      <c r="F113" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G113" s="6" t="s">
+      <c r="G113" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H113" t="s">
@@ -4024,7 +3525,7 @@
       <c r="F114" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G114" s="6" t="s">
+      <c r="G114" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H114" s="3" t="s">
@@ -4044,37 +3545,36 @@
       <c r="D116" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="E116" s="10" t="s">
         <v>161</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G116" s="2" t="str">
-        <f>VLOOKUP(B116,[1]Hoja1!B:D,3,0)</f>
-        <v>Told II</v>
+      <c r="G116" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
+      <c r="B117" s="18"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B118" s="7"/>
-      <c r="C118" s="6"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I119" s="6"/>
+      <c r="I119" s="5"/>
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
@@ -4082,7 +3582,7 @@
       </c>
       <c r="B120"/>
       <c r="D120" s="3"/>
-      <c r="G120" s="10"/>
+      <c r="G120" s="9"/>
     </row>
     <row r="121" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
@@ -4093,16 +3593,16 @@
       <c r="A123" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="5"/>
+      <c r="B123" s="18"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="18"/>
     </row>
     <row r="124" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="6"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
@@ -4128,16 +3628,16 @@
       <c r="A129" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
     </row>
     <row r="130" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B130" s="7"/>
-      <c r="C130" s="6"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
@@ -4155,36 +3655,36 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:29" s="15" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="12"/>
-      <c r="B135" s="13"/>
-      <c r="C135" s="13"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="13"/>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="13"/>
-      <c r="J135" s="13"/>
-      <c r="K135" s="13"/>
-      <c r="L135" s="13"/>
-      <c r="M135" s="13"/>
-      <c r="N135" s="13"/>
-      <c r="O135" s="13"/>
-      <c r="P135" s="13"/>
-      <c r="Q135" s="13"/>
-      <c r="R135" s="13"/>
-      <c r="S135" s="13"/>
-      <c r="T135" s="13"/>
-      <c r="U135" s="13"/>
-      <c r="V135" s="13"/>
-      <c r="W135" s="13"/>
-      <c r="X135" s="13"/>
-      <c r="Y135" s="13"/>
-      <c r="Z135" s="13"/>
-      <c r="AA135" s="13"/>
-      <c r="AB135" s="13"/>
-      <c r="AC135" s="13"/>
+    <row r="135" spans="1:29" s="14" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="11"/>
+      <c r="B135" s="12"/>
+      <c r="C135" s="12"/>
+      <c r="D135" s="13"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="12"/>
+      <c r="I135" s="12"/>
+      <c r="J135" s="12"/>
+      <c r="K135" s="12"/>
+      <c r="L135" s="12"/>
+      <c r="M135" s="12"/>
+      <c r="N135" s="12"/>
+      <c r="O135" s="12"/>
+      <c r="P135" s="12"/>
+      <c r="Q135" s="12"/>
+      <c r="R135" s="12"/>
+      <c r="S135" s="12"/>
+      <c r="T135" s="12"/>
+      <c r="U135" s="12"/>
+      <c r="V135" s="12"/>
+      <c r="W135" s="12"/>
+      <c r="X135" s="12"/>
+      <c r="Y135" s="12"/>
+      <c r="Z135" s="12"/>
+      <c r="AA135" s="12"/>
+      <c r="AB135" s="12"/>
+      <c r="AC135" s="12"/>
     </row>
     <row r="136" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
@@ -4202,29 +3702,28 @@
       <c r="F136" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G136" s="2" t="str">
-        <f>VLOOKUP(B136,[1]Hoja1!B:D,3,0)</f>
-        <v>Systematics-Impacs</v>
+      <c r="G136" s="2" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="137" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B137" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C137" s="5"/>
-      <c r="D137" s="5"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
     </row>
     <row r="138" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C138" s="6"/>
+      <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
@@ -4236,16 +3735,16 @@
       <c r="C139" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D139" s="5" t="s">
         <v>168</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F139" s="6" t="s">
+      <c r="F139" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G139" s="6" t="s">
+      <c r="G139" s="5" t="s">
         <v>171</v>
       </c>
       <c r="H139" s="3" t="s">
@@ -4262,16 +3761,16 @@
       <c r="C140" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="5" t="s">
         <v>173</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F140" s="6" t="s">
+      <c r="F140" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G140" s="6" t="s">
+      <c r="G140" s="5" t="s">
         <v>175</v>
       </c>
       <c r="H140" s="3" t="s">
@@ -4288,13 +3787,13 @@
       <c r="C141" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D141" s="5" t="s">
         <v>176</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="F141" s="5" t="s">
         <v>177</v>
       </c>
       <c r="G141" s="3" t="s">
@@ -4308,17 +3807,17 @@
       <c r="A143" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B143" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C143" s="5"/>
-      <c r="D143" s="5"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="18"/>
     </row>
     <row r="144" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B144" s="6" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4332,16 +3831,16 @@
       <c r="C145" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="D145" s="5" t="s">
         <v>170</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F145" s="6" t="s">
+      <c r="F145" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G145" s="5" t="s">
         <v>182</v>
       </c>
       <c r="H145" s="3" t="s">
@@ -4358,16 +3857,16 @@
       <c r="C146" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="5" t="s">
         <v>173</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F146" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G146" s="5" t="s">
         <v>175</v>
       </c>
       <c r="H146" s="3" t="s">
@@ -4384,13 +3883,13 @@
       <c r="C147" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="D147" s="5" t="s">
         <v>176</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F147" s="6" t="s">
+      <c r="F147" s="5" t="s">
         <v>177</v>
       </c>
       <c r="G147" s="3" t="s">
@@ -4404,20 +3903,20 @@
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="18"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
@@ -4429,16 +3928,16 @@
       <c r="C151" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="D151" s="5" t="s">
         <v>170</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F151" s="6" t="s">
+      <c r="F151" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G151" s="6" t="s">
+      <c r="G151" s="5" t="s">
         <v>186</v>
       </c>
       <c r="H151" s="3" t="s">
@@ -4455,16 +3954,16 @@
       <c r="C152" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D152" s="6" t="s">
+      <c r="D152" s="5" t="s">
         <v>173</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F152" s="6" t="s">
+      <c r="F152" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G152" s="6" t="s">
+      <c r="G152" s="5" t="s">
         <v>175</v>
       </c>
       <c r="H152" s="3" t="s">
@@ -4481,13 +3980,13 @@
       <c r="C153" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="D153" s="5" t="s">
         <v>176</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F153" s="6" t="s">
+      <c r="F153" s="5" t="s">
         <v>177</v>
       </c>
       <c r="G153" s="3" t="s">
@@ -4513,29 +4012,28 @@
       <c r="F155" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G155" s="2" t="str">
-        <f>VLOOKUP(B155,[1]Hoja1!B:D,3,0)</f>
-        <v>Systematics-Saving Times</v>
+      <c r="G155" s="2" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="18"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B157" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C157" s="6"/>
+      <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
@@ -4547,16 +4045,16 @@
       <c r="C158" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="D158" s="5" t="s">
         <v>191</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F158" s="6" t="s">
+      <c r="F158" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G158" s="6" t="s">
+      <c r="G158" s="5" t="s">
         <v>194</v>
       </c>
     </row>
@@ -4570,16 +4068,16 @@
       <c r="C159" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D159" s="6" t="s">
+      <c r="D159" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F159" s="6" t="s">
+      <c r="F159" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G159" s="6" t="s">
+      <c r="G159" s="5" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4593,13 +4091,13 @@
       <c r="C160" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D160" s="6" t="s">
+      <c r="D160" s="5" t="s">
         <v>197</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F160" s="6" t="s">
+      <c r="F160" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G160" s="3" t="s">
@@ -4610,20 +4108,20 @@
       <c r="A162" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C162" s="5"/>
-      <c r="D162" s="5"/>
+      <c r="C162" s="18"/>
+      <c r="D162" s="18"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C163" s="6"/>
+      <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
@@ -4635,16 +4133,16 @@
       <c r="C164" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D164" s="6" t="s">
+      <c r="D164" s="5" t="s">
         <v>191</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F164" s="6" t="s">
+      <c r="F164" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G164" s="6" t="s">
+      <c r="G164" s="5" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4658,16 +4156,16 @@
       <c r="C165" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D165" s="6" t="s">
+      <c r="D165" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F165" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G165" s="6" t="s">
+      <c r="G165" s="5" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4681,13 +4179,13 @@
       <c r="C166" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D166" s="6" t="s">
+      <c r="D166" s="5" t="s">
         <v>197</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F166" s="6" t="s">
+      <c r="F166" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G166" s="3" t="s">
@@ -4698,20 +4196,20 @@
       <c r="A168" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C168" s="5"/>
-      <c r="D168" s="5"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="18"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B169" s="7" t="s">
+      <c r="B169" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="C169" s="6"/>
+      <c r="C169" s="5"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
@@ -4723,16 +4221,16 @@
       <c r="C170" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D170" s="6" t="s">
+      <c r="D170" s="5" t="s">
         <v>191</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F170" s="6" t="s">
+      <c r="F170" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G170" s="6" t="s">
+      <c r="G170" s="5" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4746,16 +4244,16 @@
       <c r="C171" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D171" s="6" t="s">
+      <c r="D171" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F171" s="6" t="s">
+      <c r="F171" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G171" s="6" t="s">
+      <c r="G171" s="5" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4769,13 +4267,13 @@
       <c r="C172" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D172" s="6" t="s">
+      <c r="D172" s="5" t="s">
         <v>197</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F172" s="6" t="s">
+      <c r="F172" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G172" s="3" t="s">
@@ -4795,35 +4293,34 @@
       <c r="D174" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E174" s="11" t="s">
+      <c r="E174" s="10" t="s">
         <v>207</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G174" s="2" t="str">
-        <f>VLOOKUP(B174,[1]Hoja1!B:D,3,0)</f>
-        <v>BankTrade</v>
+      <c r="G174" s="2" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
+      <c r="C175" s="18"/>
+      <c r="D175" s="18"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C176" s="6"/>
+      <c r="C176" s="5"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
@@ -4835,22 +4332,22 @@
       <c r="C177" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D177" s="6" t="s">
+      <c r="D177" s="5" t="s">
         <v>211</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F177" s="6" t="s">
+      <c r="F177" s="5" t="s">
         <v>205</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="H177" s="6" t="s">
+      <c r="H177" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I177" s="6" t="s">
+      <c r="I177" s="5" t="s">
         <v>211</v>
       </c>
       <c r="J177" s="3" t="s">
@@ -4867,22 +4364,22 @@
       <c r="C178" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D178" s="6" t="s">
+      <c r="D178" s="5" t="s">
         <v>214</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F178" s="6" t="s">
+      <c r="F178" s="5" t="s">
         <v>215</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H178" s="6" t="s">
+      <c r="H178" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="I178" s="6" t="s">
+      <c r="I178" s="5" t="s">
         <v>214</v>
       </c>
       <c r="J178" s="3" t="s">
@@ -4899,19 +4396,19 @@
       <c r="C179" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D179" s="6" t="s">
+      <c r="D179" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F179" s="6" t="s">
+      <c r="F179" s="5" t="s">
         <v>217</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H179" s="6" t="s">
+      <c r="H179" s="5" t="s">
         <v>218</v>
       </c>
       <c r="I179" s="3" t="s">
@@ -4922,28 +4419,28 @@
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H180" s="6"/>
+      <c r="H180" s="5"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
-      <c r="H181" s="6"/>
+      <c r="C181" s="18"/>
+      <c r="D181" s="18"/>
+      <c r="H181" s="5"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B182" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C182" s="6"/>
-      <c r="H182" s="6"/>
+      <c r="C182" s="5"/>
+      <c r="H182" s="5"/>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
@@ -4955,22 +4452,22 @@
       <c r="C183" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D183" s="6" t="s">
+      <c r="D183" s="5" t="s">
         <v>223</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F183" s="6" t="s">
+      <c r="F183" s="5" t="s">
         <v>205</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H183" s="6" t="s">
+      <c r="H183" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I183" s="6" t="s">
+      <c r="I183" s="5" t="s">
         <v>223</v>
       </c>
       <c r="J183" s="3" t="s">
@@ -4987,22 +4484,22 @@
       <c r="C184" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D184" s="6" t="s">
+      <c r="D184" s="5" t="s">
         <v>214</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F184" s="6" t="s">
+      <c r="F184" s="5" t="s">
         <v>215</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H184" s="6" t="s">
+      <c r="H184" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="I184" s="6" t="s">
+      <c r="I184" s="5" t="s">
         <v>214</v>
       </c>
       <c r="J184" s="3" t="s">
@@ -5019,19 +4516,19 @@
       <c r="C185" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D185" s="6" t="s">
+      <c r="D185" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F185" s="6" t="s">
+      <c r="F185" s="5" t="s">
         <v>217</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H185" s="6" t="s">
+      <c r="H185" s="5" t="s">
         <v>218</v>
       </c>
       <c r="I185" s="3" t="s">
@@ -5042,28 +4539,28 @@
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H186" s="6"/>
+      <c r="H186" s="5"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B187" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C187" s="5"/>
-      <c r="D187" s="5"/>
-      <c r="H187" s="6"/>
+      <c r="C187" s="18"/>
+      <c r="D187" s="18"/>
+      <c r="H187" s="5"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C188" s="6"/>
-      <c r="H188" s="6"/>
+      <c r="C188" s="5"/>
+      <c r="H188" s="5"/>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
@@ -5075,22 +4572,22 @@
       <c r="C189" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D189" s="6" t="s">
+      <c r="D189" s="5" t="s">
         <v>227</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="F189" s="6" t="s">
+      <c r="F189" s="5" t="s">
         <v>205</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H189" s="6" t="s">
+      <c r="H189" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I189" s="6" t="s">
+      <c r="I189" s="5" t="s">
         <v>227</v>
       </c>
       <c r="J189" s="3" t="s">
@@ -5107,22 +4604,22 @@
       <c r="C190" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D190" s="6" t="s">
+      <c r="D190" s="5" t="s">
         <v>214</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F190" s="6" t="s">
+      <c r="F190" s="5" t="s">
         <v>215</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H190" s="6" t="s">
+      <c r="H190" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="I190" s="6" t="s">
+      <c r="I190" s="5" t="s">
         <v>214</v>
       </c>
       <c r="J190" s="3" t="s">
@@ -5139,19 +4636,19 @@
       <c r="C191" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D191" s="6" t="s">
+      <c r="D191" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F191" s="6" t="s">
+      <c r="F191" s="5" t="s">
         <v>217</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H191" s="6" t="s">
+      <c r="H191" s="5" t="s">
         <v>218</v>
       </c>
       <c r="I191" s="3" t="s">
@@ -5177,29 +4674,28 @@
       <c r="F193" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G193" s="2" t="str">
-        <f>VLOOKUP(B193,[1]Hoja1!B:D,3,0)</f>
-        <v>Sistema de Administración de Tarjetas - NSAT</v>
+      <c r="G193" s="2" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B194" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="C194" s="5"/>
-      <c r="D194" s="5"/>
+      <c r="C194" s="18"/>
+      <c r="D194" s="18"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C195" s="6"/>
+      <c r="C195" s="5"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
@@ -5217,7 +4713,7 @@
       <c r="E196" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F196" s="6" t="s">
+      <c r="F196" s="5" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5237,7 +4733,7 @@
       <c r="E197" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F197" s="6" t="s">
+      <c r="F197" s="5" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5251,13 +4747,13 @@
       <c r="C198" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D198" s="6" t="s">
+      <c r="D198" s="5" t="s">
         <v>239</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F198" s="6" t="s">
+      <c r="F198" s="5" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5265,20 +4761,20 @@
       <c r="A200" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="B200" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
+      <c r="C200" s="18"/>
+      <c r="D200" s="18"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C201" s="6"/>
+      <c r="C201" s="5"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
@@ -5296,7 +4792,7 @@
       <c r="E202" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F202" s="6" t="s">
+      <c r="F202" s="5" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5316,7 +4812,7 @@
       <c r="E203" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F203" s="6" t="s">
+      <c r="F203" s="5" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5330,13 +4826,13 @@
       <c r="C204" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D204" s="6" t="s">
+      <c r="D204" s="5" t="s">
         <v>239</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F204" s="6" t="s">
+      <c r="F204" s="5" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5344,20 +4840,20 @@
       <c r="A206" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="B206" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="C206" s="5"/>
-      <c r="D206" s="5"/>
+      <c r="C206" s="18"/>
+      <c r="D206" s="18"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C207" s="6"/>
+      <c r="C207" s="5"/>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
@@ -5375,7 +4871,7 @@
       <c r="E208" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F208" s="6" t="s">
+      <c r="F208" s="5" t="s">
         <v>236</v>
       </c>
     </row>
@@ -5395,7 +4891,7 @@
       <c r="E209" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F209" s="6" t="s">
+      <c r="F209" s="5" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5409,13 +4905,13 @@
       <c r="C210" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D210" s="6" t="s">
+      <c r="D210" s="5" t="s">
         <v>239</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F210" s="6" t="s">
+      <c r="F210" s="5" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5435,29 +4931,28 @@
       <c r="F212" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G212" s="2" t="str">
-        <f>VLOOKUP(B212,[1]Hoja1!B:D,3,0)</f>
-        <v>Financiamiento de cobranza de documentos</v>
+      <c r="G212" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="B213" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
+      <c r="C213" s="18"/>
+      <c r="D213" s="18"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C214" s="6"/>
+      <c r="C214" s="5"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
@@ -5475,10 +4970,10 @@
       <c r="E215" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F215" s="6" t="s">
+      <c r="F215" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G215" s="6" t="s">
+      <c r="G215" s="5" t="s">
         <v>255</v>
       </c>
       <c r="H215" s="3" t="s">
@@ -5519,10 +5014,10 @@
       <c r="E216" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F216" s="6" t="s">
+      <c r="F216" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G216" s="6" t="s">
+      <c r="G216" s="5" t="s">
         <v>262</v>
       </c>
       <c r="H216" s="3" t="s">
@@ -5563,10 +5058,10 @@
       <c r="E217" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F217" s="6" t="s">
+      <c r="F217" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G217" s="6" t="s">
+      <c r="G217" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H217" s="3" t="s">
@@ -5595,17 +5090,17 @@
       <c r="A219" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="B219" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
+      <c r="C219" s="18"/>
+      <c r="D219" s="18"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="6" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5625,10 +5120,10 @@
       <c r="E221" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F221" s="6" t="s">
+      <c r="F221" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G221" s="6" t="s">
+      <c r="G221" s="5" t="s">
         <v>255</v>
       </c>
       <c r="H221" s="3" t="s">
@@ -5669,10 +5164,10 @@
       <c r="E222" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F222" s="6" t="s">
+      <c r="F222" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G222" s="6" t="s">
+      <c r="G222" s="5" t="s">
         <v>262</v>
       </c>
       <c r="H222" s="3" t="s">
@@ -5713,10 +5208,10 @@
       <c r="E223" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F223" s="6" t="s">
+      <c r="F223" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G223" s="6" t="s">
+      <c r="G223" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H223" s="3" t="s">
@@ -5745,17 +5240,17 @@
       <c r="A225" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="C225" s="5"/>
-      <c r="D225" s="5"/>
+      <c r="C225" s="18"/>
+      <c r="D225" s="18"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="6" t="s">
         <v>271</v>
       </c>
     </row>
@@ -5775,10 +5270,10 @@
       <c r="E227" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F227" s="6" t="s">
+      <c r="F227" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G227" s="6" t="s">
+      <c r="G227" s="5" t="s">
         <v>255</v>
       </c>
       <c r="H227" s="3" t="s">
@@ -5819,10 +5314,10 @@
       <c r="E228" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F228" s="6" t="s">
+      <c r="F228" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G228" s="6" t="s">
+      <c r="G228" s="5" t="s">
         <v>262</v>
       </c>
       <c r="H228" s="3" t="s">
@@ -5863,10 +5358,10 @@
       <c r="E229" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F229" s="6" t="s">
+      <c r="F229" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G229" s="6" t="s">
+      <c r="G229" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H229" s="3" t="s">
@@ -5904,44 +5399,43 @@
       <c r="D231" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E231" s="11" t="s">
+      <c r="E231" s="10" t="s">
         <v>161</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G231" s="2" t="str">
-        <f>VLOOKUP(B231,[1]Hoja1!B:D,3,0)</f>
-        <v>Garantías y custodia</v>
+      <c r="G231" s="2" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5"/>
-      <c r="D232" s="5"/>
+      <c r="B232" s="18"/>
+      <c r="C232" s="18"/>
+      <c r="D232" s="18"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B233" s="7"/>
-      <c r="C233" s="6"/>
+      <c r="B233" s="6"/>
+      <c r="C233" s="5"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C234" s="6"/>
+      <c r="C234" s="5"/>
       <c r="D234" s="3"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C235" s="6"/>
+      <c r="C235" s="5"/>
       <c r="D235" s="3"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.35">
@@ -5953,16 +5447,16 @@
       <c r="A238" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
+      <c r="B238" s="18"/>
+      <c r="C238" s="18"/>
+      <c r="D238" s="18"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B239" s="7"/>
-      <c r="C239" s="6"/>
+      <c r="B239" s="6"/>
+      <c r="C239" s="5"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
@@ -5983,16 +5477,16 @@
       <c r="A244" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B244" s="5"/>
-      <c r="C244" s="5"/>
-      <c r="D244" s="5"/>
+      <c r="B244" s="18"/>
+      <c r="C244" s="18"/>
+      <c r="D244" s="18"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B245" s="7"/>
-      <c r="C245" s="6"/>
+      <c r="B245" s="6"/>
+      <c r="C245" s="5"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
@@ -6025,29 +5519,28 @@
       <c r="F250" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G250" s="2" t="str">
-        <f>VLOOKUP(B250,[1]Hoja1!B:D,3,0)</f>
-        <v>Judicial Condonación y Castigo</v>
+      <c r="G250" s="2" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B251" s="5" t="s">
+      <c r="B251" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="C251" s="5"/>
-      <c r="D251" s="5"/>
+      <c r="C251" s="18"/>
+      <c r="D251" s="18"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B252" s="7" t="s">
+      <c r="B252" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C252" s="6"/>
+      <c r="C252" s="5"/>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
@@ -6059,16 +5552,16 @@
       <c r="C253" s="3">
         <v>47706811</v>
       </c>
-      <c r="D253" s="6" t="s">
+      <c r="D253" s="5" t="s">
         <v>282</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F253" s="6">
+      <c r="F253" s="5">
         <v>846</v>
       </c>
-      <c r="G253" s="6" t="s">
+      <c r="G253" s="5" t="s">
         <v>284</v>
       </c>
       <c r="H253" s="3" t="s">
@@ -6097,16 +5590,16 @@
       <c r="C254" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D254" s="6" t="s">
+      <c r="D254" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F254" s="6" t="s">
+      <c r="F254" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G254" s="6" t="s">
+      <c r="G254" s="5" t="s">
         <v>98</v>
       </c>
       <c r="H254" s="3" t="s">
@@ -6135,16 +5628,16 @@
       <c r="C255" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D255" s="6" t="s">
+      <c r="D255" s="5" t="s">
         <v>292</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F255" s="6" t="s">
+      <c r="F255" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G255" s="6" t="s">
+      <c r="G255" s="5" t="s">
         <v>240</v>
       </c>
       <c r="H255" s="3" t="s">
@@ -6167,20 +5660,20 @@
       <c r="A257" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B257" s="5" t="s">
+      <c r="B257" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="C257" s="5"/>
-      <c r="D257" s="5"/>
+      <c r="C257" s="18"/>
+      <c r="D257" s="18"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B258" s="7" t="s">
+      <c r="B258" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C258" s="6"/>
+      <c r="C258" s="5"/>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
@@ -6192,16 +5685,16 @@
       <c r="C259" s="3">
         <v>47651226</v>
       </c>
-      <c r="D259" s="6" t="s">
+      <c r="D259" s="5" t="s">
         <v>282</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F259" s="6">
+      <c r="F259" s="5">
         <v>205</v>
       </c>
-      <c r="G259" s="6" t="s">
+      <c r="G259" s="5" t="s">
         <v>284</v>
       </c>
       <c r="H259" s="3" t="s">
@@ -6230,16 +5723,16 @@
       <c r="C260" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D260" s="6" t="s">
+      <c r="D260" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F260" s="6" t="s">
+      <c r="F260" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G260" s="6" t="s">
+      <c r="G260" s="5" t="s">
         <v>98</v>
       </c>
       <c r="H260" s="3" t="s">
@@ -6268,16 +5761,16 @@
       <c r="C261" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D261" s="6" t="s">
+      <c r="D261" s="5" t="s">
         <v>292</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F261" s="6" t="s">
+      <c r="F261" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G261" s="6" t="s">
+      <c r="G261" s="5" t="s">
         <v>240</v>
       </c>
       <c r="H261" s="3" t="s">
@@ -6300,20 +5793,20 @@
       <c r="A263" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B263" s="5" t="s">
+      <c r="B263" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="C263" s="5"/>
-      <c r="D263" s="5"/>
+      <c r="C263" s="18"/>
+      <c r="D263" s="18"/>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B264" s="7" t="s">
+      <c r="B264" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C264" s="6"/>
+      <c r="C264" s="5"/>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
@@ -6325,16 +5818,16 @@
       <c r="C265" s="3">
         <v>47683862</v>
       </c>
-      <c r="D265" s="6" t="s">
+      <c r="D265" s="5" t="s">
         <v>282</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F265" s="6">
+      <c r="F265" s="5">
         <v>852</v>
       </c>
-      <c r="G265" s="6" t="s">
+      <c r="G265" s="5" t="s">
         <v>284</v>
       </c>
       <c r="H265" s="3" t="s">
@@ -6363,16 +5856,16 @@
       <c r="C266" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D266" s="6" t="s">
+      <c r="D266" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F266" s="6" t="s">
+      <c r="F266" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G266" s="6" t="s">
+      <c r="G266" s="5" t="s">
         <v>98</v>
       </c>
       <c r="H266" s="3" t="s">
@@ -6401,16 +5894,16 @@
       <c r="C267" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D267" s="6" t="s">
+      <c r="D267" s="5" t="s">
         <v>292</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F267" s="6" t="s">
+      <c r="F267" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G267" s="6" t="s">
+      <c r="G267" s="5" t="s">
         <v>240</v>
       </c>
       <c r="H267" s="3" t="s">
@@ -6448,59 +5941,58 @@
       <c r="F269" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G269" s="2" t="str">
-        <f>VLOOKUP(B269,[1]Hoja1!B:D,3,0)</f>
-        <v>Hipotecario y créditos de consumo</v>
+      <c r="G269" s="2" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="B270" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="C270" s="5"/>
-      <c r="D270" s="5"/>
+      <c r="C270" s="18"/>
+      <c r="D270" s="18"/>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B271" s="7" t="s">
+      <c r="B271" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C271" s="6"/>
+      <c r="C271" s="5"/>
     </row>
     <row r="272" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="16" t="s">
+      <c r="A272" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B272" s="17" t="s">
+      <c r="B272" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="C272" s="17" t="s">
+      <c r="C272" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="D272" s="17" t="s">
+      <c r="D272" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="E272" s="17" t="s">
+      <c r="E272" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="F272" s="17" t="s">
+      <c r="F272" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="G272" s="17" t="s">
+      <c r="G272" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="H272" s="17" t="s">
+      <c r="H272" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="I272" s="17" t="s">
+      <c r="I272" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="J272" s="17" t="s">
+      <c r="J272" s="16" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6514,16 +6006,16 @@
       <c r="C273" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D273" s="6" t="s">
+      <c r="D273" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F273" s="6" t="s">
+      <c r="F273" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G273" s="6" t="s">
+      <c r="G273" s="5" t="s">
         <v>55</v>
       </c>
       <c r="H273" s="3" t="s">
@@ -6546,16 +6038,16 @@
       <c r="C274" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D274" s="6" t="s">
+      <c r="D274" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F274" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G274" s="6" t="s">
+      <c r="F274" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G274" s="5" t="s">
         <v>101</v>
       </c>
       <c r="H274" s="3" t="s">
@@ -6572,20 +6064,20 @@
       <c r="A276" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B276" s="5" t="s">
+      <c r="B276" s="18" t="s">
         <v>317</v>
       </c>
-      <c r="C276" s="5"/>
-      <c r="D276" s="5"/>
+      <c r="C276" s="18"/>
+      <c r="D276" s="18"/>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B277" s="7" t="s">
+      <c r="B277" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="C277" s="6"/>
+      <c r="C277" s="5"/>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
@@ -6597,16 +6089,16 @@
       <c r="C278" t="s">
         <v>320</v>
       </c>
-      <c r="D278" s="6" t="s">
+      <c r="D278" s="5" t="s">
         <v>321</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F278" s="6" t="s">
+      <c r="F278" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G278" s="18" t="s">
+      <c r="G278" s="17" t="s">
         <v>170</v>
       </c>
       <c r="H278" t="s">
@@ -6629,16 +6121,16 @@
       <c r="C279" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D279" s="6" t="s">
+      <c r="D279" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F279" s="6" t="s">
+      <c r="F279" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G279" s="6" t="s">
+      <c r="G279" s="5" t="s">
         <v>55</v>
       </c>
       <c r="H279" s="3" t="s">
@@ -6661,16 +6153,16 @@
       <c r="C280" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D280" s="6" t="s">
+      <c r="D280" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F280" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G280" s="6" t="s">
+      <c r="F280" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G280" s="5" t="s">
         <v>101</v>
       </c>
       <c r="H280" s="3" t="s">
@@ -6687,20 +6179,20 @@
       <c r="A282" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B282" s="5" t="s">
+      <c r="B282" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="C282" s="5"/>
-      <c r="D282" s="5"/>
+      <c r="C282" s="18"/>
+      <c r="D282" s="18"/>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B283" s="7" t="s">
+      <c r="B283" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="C283" s="6"/>
+      <c r="C283" s="5"/>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
@@ -6712,16 +6204,16 @@
       <c r="C284" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D284" s="6" t="s">
+      <c r="D284" s="5" t="s">
         <v>52</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F284" s="6" t="s">
+      <c r="F284" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G284" s="6" t="s">
+      <c r="G284" s="5" t="s">
         <v>170</v>
       </c>
       <c r="H284" s="3" t="s">
@@ -6744,13 +6236,13 @@
       <c r="C285" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D285" s="6" t="s">
+      <c r="D285" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E285" t="s">
         <v>238</v>
       </c>
-      <c r="F285" s="6" t="s">
+      <c r="F285" s="5" t="s">
         <v>28</v>
       </c>
       <c r="G285" t="s">
@@ -6776,16 +6268,16 @@
       <c r="C286" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D286" s="6" t="s">
+      <c r="D286" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F286" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G286" s="6" t="s">
+      <c r="F286" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G286" s="5" t="s">
         <v>101</v>
       </c>
       <c r="H286" s="3" t="s">
@@ -6800,6 +6292,42 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B110:D110"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="B137:D137"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="B225:D225"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="B162:D162"/>
+    <mergeCell ref="B168:D168"/>
+    <mergeCell ref="B175:D175"/>
+    <mergeCell ref="B181:D181"/>
+    <mergeCell ref="B187:D187"/>
+    <mergeCell ref="B194:D194"/>
+    <mergeCell ref="B200:D200"/>
+    <mergeCell ref="B206:D206"/>
+    <mergeCell ref="B213:D213"/>
+    <mergeCell ref="B219:D219"/>
     <mergeCell ref="B270:D270"/>
     <mergeCell ref="B276:D276"/>
     <mergeCell ref="B282:D282"/>
@@ -6809,42 +6337,6 @@
     <mergeCell ref="B251:D251"/>
     <mergeCell ref="B257:D257"/>
     <mergeCell ref="B263:D263"/>
-    <mergeCell ref="B194:D194"/>
-    <mergeCell ref="B200:D200"/>
-    <mergeCell ref="B206:D206"/>
-    <mergeCell ref="B213:D213"/>
-    <mergeCell ref="B219:D219"/>
-    <mergeCell ref="B225:D225"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="B162:D162"/>
-    <mergeCell ref="B168:D168"/>
-    <mergeCell ref="B175:D175"/>
-    <mergeCell ref="B181:D181"/>
-    <mergeCell ref="B187:D187"/>
-    <mergeCell ref="B117:D117"/>
-    <mergeCell ref="B123:D123"/>
-    <mergeCell ref="B129:D129"/>
-    <mergeCell ref="B137:D137"/>
-    <mergeCell ref="B143:D143"/>
-    <mergeCell ref="B149:D149"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B91:D91"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B104:D104"/>
-    <mergeCell ref="B110:D110"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
